--- a/godziny_styczen.xlsx
+++ b/godziny_styczen.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ameliadruzba/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ameliadruzba/Desktop/projekt_python_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6E45EC2-2D11-8C4B-A50A-B5E1A27E0D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618015EF-FD1F-B149-86A8-EFF528D3C4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19520" xr2:uid="{D032FEB8-47F6-9B46-BEBD-1367F55BF394}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
   <si>
     <t>ID_pracownika</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Styczeń</t>
+  </si>
+  <si>
+    <t>amelka</t>
   </si>
 </sst>
 </file>
@@ -455,8 +458,8 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>160</v>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
       <c r="D2" s="1">
         <v>46053</v>
